--- a/Mutation_Frequency_Analysis/Sequencing_freq_data.xlsx
+++ b/Mutation_Frequency_Analysis/Sequencing_freq_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mqoutlook-my.sharepoint.com/personal/jasmine_williams2_students_mq_edu_au/Documents/2025_Research_Technician_Data/250411_TB_Population/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JasmineWilliams(HDR)\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="141" documentId="11_F25DC773A252ABDACC10487339DA6CDA5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4387773-495D-4B79-B7B0-FAF167BFE6BE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2612FBF-3C82-42E8-8E30-ED812F90629F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14560" yWindow="0" windowWidth="9530" windowHeight="15370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3760" yWindow="3760" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RIF" sheetId="1" r:id="rId1"/>
@@ -723,7 +723,7 @@
         <v>3</v>
       </c>
       <c r="C27">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
